--- a/Analysed/GPT_gpt-5.3-chat-latest_naive.xlsx
+++ b/Analysed/GPT_gpt-5.3-chat-latest_naive.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,10 +693,10 @@
         <v>11</v>
       </c>
       <c r="H6" t="n">
-        <v>1.319090909090909</v>
+        <v>1.320909090909091</v>
       </c>
       <c r="I6" t="n">
-        <v>1.771314355345924</v>
+        <v>1.771334884409854</v>
       </c>
       <c r="J6" t="n">
         <v>0.3</v>
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3902777777777778</v>
+        <v>0.4032432432432432</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5977295003223076</v>
+        <v>0.6066968609454652</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="10">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2783333333333333</v>
+        <v>0.2569230769230769</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5161395160225576</v>
+        <v>0.49589080683926</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -1570,16 +1570,16 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H26" t="n">
-        <v>1.192419354838712</v>
+        <v>1.209206349206351</v>
       </c>
       <c r="I26" t="n">
-        <v>1.409179010584168</v>
+        <v>1.426401844580351</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2357723577235772</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="27">
@@ -1878,16 +1878,16 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H33" t="n">
-        <v>3.031428571428569</v>
+        <v>2.849333333333331</v>
       </c>
       <c r="I33" t="n">
-        <v>3.528982046669304</v>
+        <v>3.410200385119129</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.2142857142857143</v>
       </c>
     </row>
     <row r="34">
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H37" t="n">
-        <v>3.890476190476191</v>
+        <v>2.783333333333332</v>
       </c>
       <c r="I37" t="n">
-        <v>4.353925431913906</v>
+        <v>3.644402100025008</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7</v>
+        <v>0.7931034482758621</v>
       </c>
     </row>
     <row r="38">
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H42" t="n">
-        <v>9.105999999999998</v>
+        <v>9.069090909090908</v>
       </c>
       <c r="I42" t="n">
-        <v>9.706902698595467</v>
+        <v>9.619722165710117</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="43">
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H43" t="n">
-        <v>10.48166666666667</v>
+        <v>11.15571428571429</v>
       </c>
       <c r="I43" t="n">
-        <v>11.42054566705695</v>
+        <v>12.03348411724551</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44">
@@ -2358,20 +2358,20 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>116</v>
+        <v>205</v>
       </c>
       <c r="H44" t="n">
-        <v>6.391896551724138</v>
+        <v>42.64512195121952</v>
       </c>
       <c r="I44" t="n">
-        <v>7.696514997285999</v>
+        <v>42.91268085366819</v>
       </c>
       <c r="J44" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.1274509803921569</v>
       </c>
     </row>
     <row r="45">
@@ -2402,20 +2402,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="H45" t="n">
-        <v>7.023888888888887</v>
+        <v>6.391896551724138</v>
       </c>
       <c r="I45" t="n">
-        <v>8.332493757706764</v>
+        <v>7.696514997285999</v>
       </c>
       <c r="J45" t="n">
-        <v>0.303370786516854</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="46">
@@ -2446,20 +2446,20 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="H46" t="n">
-        <v>7.869285714285715</v>
+        <v>7.023888888888887</v>
       </c>
       <c r="I46" t="n">
-        <v>9.159911493646028</v>
+        <v>8.332493757706764</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2909090909090909</v>
+        <v>0.303370786516854</v>
       </c>
     </row>
     <row r="47">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="H47" t="n">
-        <v>39.75777777777778</v>
+        <v>7.869285714285715</v>
       </c>
       <c r="I47" t="n">
-        <v>40.22427542334769</v>
+        <v>9.159911493646028</v>
       </c>
       <c r="J47" t="n">
-        <v>0.25</v>
+        <v>0.2909090909090909</v>
       </c>
     </row>
     <row r="48">
@@ -2529,25 +2529,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OPENING</t>
+          <t>OPENING-CLOSING</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>316</v>
+        <v>9</v>
       </c>
       <c r="H48" t="n">
-        <v>8.070411392405061</v>
+        <v>39.75777777777778</v>
       </c>
       <c r="I48" t="n">
-        <v>9.41521366819264</v>
+        <v>40.22427542334769</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="49">
@@ -2578,20 +2578,20 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>195</v>
+        <v>316</v>
       </c>
       <c r="H49" t="n">
-        <v>8.267128205128206</v>
+        <v>8.070411392405061</v>
       </c>
       <c r="I49" t="n">
-        <v>9.617352293027698</v>
+        <v>9.41521366819264</v>
       </c>
       <c r="J49" t="n">
-        <v>0.06701030927835051</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="50">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="H50" t="n">
-        <v>3.07036036036036</v>
+        <v>8.510449999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>3.470377994314657</v>
+        <v>9.913683901557484</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.09045226130653267</v>
       </c>
     </row>
     <row r="51">
@@ -2666,20 +2666,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
+          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="H51" t="n">
-        <v>47.25812500000001</v>
+        <v>3.07036036036036</v>
       </c>
       <c r="I51" t="n">
-        <v>48.19557662535017</v>
+        <v>3.470377994314657</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="52">
@@ -2710,20 +2710,20 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>11.48122448979592</v>
+        <v>48.10176470588236</v>
       </c>
       <c r="I52" t="n">
-        <v>14.02528445635356</v>
+        <v>49.08550624705231</v>
       </c>
       <c r="J52" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="53">
@@ -2754,19 +2754,63 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>50</v>
+      </c>
+      <c r="H53" t="n">
+        <v>11.7154</v>
+      </c>
+      <c r="I53" t="n">
+        <v>14.26639246621233</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.6326530612244898</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gpt-5.3-chat-latest</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3.- Analog Depth Gauge_without vernier</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>OPENING_OPENING_V6_10 divisions_per_second</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="G54" t="n">
         <v>31</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H54" t="n">
         <v>10.03354838709677</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I54" t="n">
         <v>13.31320445659969</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J54" t="n">
         <v>0.5666666666666667</v>
       </c>
     </row>
@@ -2813,14 +2857,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8041</v>
+        <v>8.474299999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>12.6507</v>
+        <v>13.4715</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.8041 ± 12.6507</t>
+          <t>8.4743 ± 13.4715</t>
         </is>
       </c>
     </row>
@@ -2831,14 +2875,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.415800000000001</v>
+        <v>9.087999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>12.7689</v>
+        <v>13.5645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.4158 ± 12.7689</t>
+          <t>9.0880 ± 13.5645</t>
         </is>
       </c>
     </row>
@@ -2849,14 +2893,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4916</v>
+        <v>0.4838</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2499</v>
+        <v>0.2481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.4916 ± 0.2499</t>
+          <t>0.4838 ± 0.2481</t>
         </is>
       </c>
     </row>
@@ -2931,10 +2975,10 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5103</v>
+        <v>1.5106</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3751</v>
+        <v>0.3748</v>
       </c>
       <c r="F2" t="n">
         <v>1.8839</v>
@@ -2991,19 +3035,19 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4195</v>
+        <v>0.4181</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1063</v>
+        <v>0.1122</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.6115</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6343</v>
+        <v>0.6325</v>
       </c>
       <c r="H4" t="n">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="5">
@@ -3051,19 +3095,19 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>8.3208</v>
+        <v>8.1059</v>
       </c>
       <c r="E6" t="n">
-        <v>15.0746</v>
+        <v>15.1672</v>
       </c>
       <c r="F6" t="n">
-        <v>8.592599999999999</v>
+        <v>8.454499999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4459</v>
+        <v>0.4715</v>
       </c>
       <c r="H6" t="n">
-        <v>46.5</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="7">
@@ -3081,19 +3125,19 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>13.2899</v>
+        <v>13.2927</v>
       </c>
       <c r="E7" t="n">
-        <v>18.8059</v>
+        <v>18.8035</v>
       </c>
       <c r="F7" t="n">
-        <v>13.431</v>
+        <v>13.4339</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4918</v>
+        <v>0.4939</v>
       </c>
       <c r="H7" t="n">
-        <v>58.3</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="8">
@@ -3111,19 +3155,19 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>15.3938</v>
+        <v>15.5</v>
       </c>
       <c r="E8" t="n">
-        <v>17.4709</v>
+        <v>17.4345</v>
       </c>
       <c r="F8" t="n">
-        <v>16.5831</v>
+        <v>16.6708</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4309</v>
+        <v>0.4036</v>
       </c>
       <c r="H8" t="n">
-        <v>63.3</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="9">
@@ -3141,19 +3185,19 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>14.6968</v>
+        <v>14.917</v>
       </c>
       <c r="E9" t="n">
-        <v>17.0044</v>
+        <v>17.3306</v>
       </c>
       <c r="F9" t="n">
-        <v>16.3395</v>
+        <v>16.5774</v>
       </c>
       <c r="G9" t="n">
-        <v>0.502</v>
+        <v>0.4947</v>
       </c>
       <c r="H9" t="n">
-        <v>119.7</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="10">
@@ -3168,22 +3212,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>15.2607</v>
+        <v>20.7376</v>
       </c>
       <c r="E10" t="n">
-        <v>26.0047</v>
+        <v>23.2391</v>
       </c>
       <c r="F10" t="n">
-        <v>16.3533</v>
+        <v>21.6652</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2654</v>
+        <v>0.2378</v>
       </c>
       <c r="H10" t="n">
-        <v>67.8</v>
+        <v>95.2</v>
       </c>
     </row>
   </sheetData>
